--- a/Assignments/Sales_Analysis.xlsx
+++ b/Assignments/Sales_Analysis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sanket Kudale\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel files\Assignments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC8A301-3664-4986-86FB-3F5531C580FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7DF30A-0DC6-4D23-83F3-9A78981F8FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{57C32BBB-059D-43B6-9C6B-75D83AF18BC4}"/>
   </bookViews>
@@ -445,22 +445,22 @@
     <t>Overall Revenue</t>
   </si>
   <si>
-    <t xml:space="preserve"> Number of Transactions</t>
-  </si>
-  <si>
     <t>Minimum Sale Value</t>
   </si>
   <si>
     <t>Maximum Sale Value</t>
   </si>
   <si>
-    <t xml:space="preserve"> Average Sale Value</t>
-  </si>
-  <si>
     <t>Day</t>
   </si>
   <si>
     <t>Current Time</t>
+  </si>
+  <si>
+    <t>Average Sale Value</t>
+  </si>
+  <si>
+    <t>Number of Transactions</t>
   </si>
 </sst>
 </file>
@@ -1156,7 +1156,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>6</v>
@@ -1288,7 +1288,7 @@
         <v>30</v>
       </c>
       <c r="J6" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="M6" s="5">
         <f>COUNT(sales)</f>
@@ -1317,7 +1317,7 @@
         <v>250</v>
       </c>
       <c r="J7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M7" s="5">
         <f>MIN(sales)</f>
@@ -1346,7 +1346,7 @@
         <v>210</v>
       </c>
       <c r="J8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M8" s="5">
         <f>MAX(sales)</f>
@@ -1375,7 +1375,7 @@
         <v>360</v>
       </c>
       <c r="J9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M9" s="5">
         <f>AVERAGE(sales)</f>
@@ -1404,11 +1404,11 @@
         <v>260</v>
       </c>
       <c r="J10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M10" s="7">
         <f ca="1">NOW()</f>
-        <v>46241.500564004629</v>
+        <v>46241.880019097225</v>
       </c>
     </row>
     <row r="11" spans="1:13">
